--- a/astro-site/public/dl/pizza-shop-business-plan/pizza-shop-startup-checklist.xlsx
+++ b/astro-site/public/dl/pizza-shop-business-plan/pizza-shop-startup-checklist.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>A wood-fired oven needs a dedicated flue to the roof with a spark arrestor, built to NFPA 96 chapter 14 and your local fire and mechanical codes. Gas needs a licensed gas contractor. An electric oven (about 16.4 kW of three-phase power for a six-pizza model) still needs a hood and exhaust for steam and grease. Only wood fire can follow the Neapolitan tradition, and VPN-certified status needs AVPN certification on top of that.</t>
+          <t>A wood-fired oven needs a dedicated flue to the roof with a spark arrestor, built to NFPA 96 (chapter 14 in recent editions: ask which edition your fire marshal enforces) and your local fire and mechanical codes. Gas needs a licensed gas contractor. An electric oven (about 16.4 kW of three-phase power for a six-pizza model) still needs a hood and exhaust for steam and grease. For VPN certification the AVPN wants a wood-fired dome oven (gas only where wood is banned and documented; never electric).</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Dining room of about 750 sq ft for 50 seats, kitchen of about 320 sq ft with the oven in view, dry wood storage, restrooms and a staff area. A neighborhood street with foot traffic on evenings and weekends, and room for a patio if your city allows one.</t>
+          <t>Dining room of about 750 sq ft for 50 seats, kitchen of about 325 sq ft with the oven in view, dry wood storage, restrooms and a staff area. A neighborhood street with foot traffic on evenings and weekends, and room for a patio if your city allows one.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Kitchen layout, electrical load, occupancy, ventilation, ADA accessibility, and the flue with its spark arrestor (NFPA 96 chapter 14). Your city may add its own mechanical, fire or air-quality rules: ask in the pre-application meeting.</t>
+          <t>Kitchen layout, electrical load, plumbing with the grease interceptor, occupancy, ventilation, ADA accessibility, and the flue with its spark arrestor (NFPA 96; chapter 14 in recent editions: ask which edition your fire marshal enforces). Your city may add its own mechanical, fire or air-quality rules: ask in the pre-application meeting.</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Zoning approval and local business license</t>
+          <t>Zoning approval, business license and beer and wine license application</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>A restaurant usually needs a city or county business license, a state sales tax permit and, depending on the zoning, a conditional use approval. Ask in the pre-application meeting which ones apply to you and in what order.</t>
+          <t>A restaurant usually needs a city or county business license, a state sales tax permit and, depending on the zoning, a conditional use approval. File the beer and wine license with your state alcohol beverage control (ABC) board and your city or county as soon as the lease is signed: it often takes 3 to 12 months. In a non-quota state the plan budgets about $3,000 inside the project line; quota states cost far more. Ask in the pre-application meeting which approvals apply to you and in what order.</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Using the public sidewalk or right-of-way is always permitted separately. Ask your city about the fee, the hours, the furniture rules and whether beer and wine can be served on the patio.</t>
+          <t>Using the public sidewalk or right-of-way usually needs its own permit. Ask your city about the fee, the hours, the furniture rules and whether beer and wine can be served on the patio.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Oak, beech, ash or olive, seasoned dry; never painted or stained wood, and never particleboard. Store it dry, ventilated and away from the oven mouth (NFPA 96 and your fire marshal set the distance), with a supplier that delivers regularly.</t>
+          <t>Oak, ash, maple, hickory or fruitwood, seasoned dry; never painted or stained wood, and never particleboard. Store it dry, ventilated and away from the oven mouth (NFPA 96 and your fire marshal set the distance), with a supplier that delivers regularly. Keep the extinguishers your fire marshal specifies within reach of the oven (for solid fuel, usually a 2-A water-type or a Class K wet-chemical unit) and a Class K extinguisher by the fryer.</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>If dough, cut toppings or cheese ever sit out of temperature control, use time as the control: write the procedure, mark each item with its discard time and get health department approval (Food Code 3-501.19). Otherwise keep cold food at 41 °F (5 °C) or below.</t>
+          <t>If dough, cut toppings or cheese ever sit out of temperature control, use time as the control: write the procedure, mark each item with its discard time and keep it on site for the health inspector (Food Code 3-501.19; some jurisdictions also ask you to submit it for approval). Otherwise keep cold food at 41 °F (5 °C) or below.</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Offer to-go boxes for what guests do not finish, at no charge, and say so on the menu. Keep boxes in stock for it.</t>
+          <t>If you offer to-go boxes for leftovers, decide whether you charge for them and keep them in stock; check your local packaging rules.</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Cost every pizza, not only the Margherita: with mozzarella di bufala, burrata or imported cured meats and the marketplace commission, your best seller can run to 25-35% food cost. Use the kit's dough and food cost calculator.</t>
+          <t>Cost every pizza, not only the Margherita: with mozzarella di bufala, burrata or imported cured meats a pizza can run at 22-28% food cost (the Bufalina comes out at about 23% in the calculator), and on marketplace orders the commission comes out of the price on top. Use the kit's dough and food cost calculator.</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Read the commission tiers (published tiers run from about 15% to 30%, plus roughly 6-10% on pickup orders through the app), the payout schedule, who pays for promotions and the tablet cost. Check the current terms before you sign. Set a ceiling: in this plan, 10% of sales.</t>
+          <t>Read the commission tiers (published tiers run from about 15% to 30%, plus roughly 6-10% on pickup orders through the app), the payout schedule, who pays for promotions and the tablet cost. Check the current terms before you sign. Set a ceiling: in this plan, 12% of sales.</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Sales, commission, promotions and boxes: if the marketplace passes 10% of sales or its margin does not cover the commission, cut back or raise prices. Own delivery only with W-2 drivers and when the volume pays for it.</t>
+          <t>Sales, commission, promotions and boxes: if the marketplace passes 12% of sales (the plan's ceiling) or its margin does not cover the commission, cut back or raise prices. Own delivery only with W-2 drivers and when the volume pays for it.</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/pizza-shop-business-plan/pizza-shop-startup-checklist.xlsx
+++ b/astro-site/public/dl/pizza-shop-business-plan/pizza-shop-startup-checklist.xlsx
@@ -953,7 +953,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Use the dropdown: ✓, —, N/A. ✓ = done, — = pending, N/A = not applicable and comes out of the total." type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Use the dropdown: ✓, ☐, N/A. ✓ = done, ☐ = pending, N/A = not applicable and comes out of the total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1463,7 +1463,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Use the dropdown: ✓, —, N/A. ✓ = done, — = pending, N/A = not applicable and comes out of the total." type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Use the dropdown: ✓, ☐, N/A. ✓ = done, ☐ = pending, N/A = not applicable and comes out of the total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1951,7 +1951,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Use the dropdown: ✓, —, N/A. ✓ = done, — = pending, N/A = not applicable and comes out of the total." type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Use the dropdown: ✓, ☐, N/A. ✓ = done, ☐ = pending, N/A = not applicable and comes out of the total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2411,7 +2411,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Use the dropdown: ✓, —, N/A. ✓ = done, — = pending, N/A = not applicable and comes out of the total." type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Use the dropdown: ✓, ☐, N/A. ✓ = done, ☐ = pending, N/A = not applicable and comes out of the total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2878,7 +2878,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Use the dropdown: ✓, —, N/A. ✓ = done, — = pending, N/A = not applicable and comes out of the total." type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Use the dropdown: ✓, ☐, N/A. ✓ = done, ☐ = pending, N/A = not applicable and comes out of the total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3334,7 +3334,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Use the dropdown: ✓, —, N/A. ✓ = done, — = pending, N/A = not applicable and comes out of the total." type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Use the dropdown: ✓, ☐, N/A. ✓ = done, ☐ = pending, N/A = not applicable and comes out of the total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
